--- a/backtest_runs/20260410_193731/by_symbol/TRIPF/TRIPF.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/TRIPF/TRIPF.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-6830.290000000017</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>93169.70999999998</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>99593.52999999998</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>99593.52999999998</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>99593.52999999998</v>
@@ -909,7 +909,7 @@
         <v>-4224.099999999998</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>95887.48</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>95887.48</v>
@@ -1047,7 +1047,7 @@
         <v>-1625.880000000005</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>100175.34</v>
@@ -1093,7 +1093,7 @@
         <v>-4574.779999999996</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>95600.56</v>
@@ -1185,7 +1185,7 @@
         <v>-4136.429999999998</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>92675.56999999999</v>
@@ -1277,7 +1277,7 @@
         <v>-7706.990000000002</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>84968.57999999999</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>84968.57999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-1753.400000000002</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>90977.95999999999</v>
@@ -1507,7 +1507,7 @@
         <v>-581.8100000000031</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>90396.14999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-39.84999999999773</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>99657.28999999999</v>
